--- a/artfynd/A 29320-2026 artfynd.xlsx
+++ b/artfynd/A 29320-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ48"/>
+  <dimension ref="A1:AZ49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2837,10 +2837,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122968537</v>
+        <v>137422894</v>
       </c>
       <c r="B18" t="n">
-        <v>56884</v>
+        <v>58876</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2848,21 +2848,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>208255</v>
+        <v>208245</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2870,41 +2870,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>på övervintringsplats</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tobokrysset, Upl</t>
+          <t>Tegelsmoraån, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>649066</v>
+        <v>648997</v>
       </c>
       <c r="R18" t="n">
-        <v>6680538</v>
+        <v>6680635</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2931,22 +2907,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2955,7 +2931,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2973,16 +2948,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122968537</t>
+          <t>https://artportalen.se/Sighting/137422894</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115538367</v>
+        <v>122968537</v>
       </c>
       <c r="B19" t="n">
-        <v>56905</v>
+        <v>56884</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2990,26 +2965,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>208260</v>
+        <v>208255</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -3029,7 +3004,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>på övervintringsplats</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -3073,7 +3048,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -3083,17 +3058,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
           <t>10:30</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Finns utmed järnvägen från korset och 300 meter utmed  traktorspåret.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3120,13 +3090,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115538367</t>
+          <t>https://artportalen.se/Sighting/122968537</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127752094</v>
+        <v>115538367</v>
       </c>
       <c r="B20" t="n">
         <v>56905</v>
@@ -3156,7 +3126,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3166,7 +3136,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -3174,16 +3149,21 @@
           <t>vilande</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tobokrysset, Tobokrysset, Upl</t>
+          <t>Tobokrysset, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>648902</v>
+        <v>649066</v>
       </c>
       <c r="R20" t="n">
-        <v>6680769</v>
+        <v>6680538</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -3210,22 +3190,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Finns utmed järnvägen från korset och 300 meter utmed  traktorspåret.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3234,6 +3219,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3251,13 +3237,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127752094</t>
+          <t>https://artportalen.se/Sighting/115538367</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127772505</v>
+        <v>127752094</v>
       </c>
       <c r="B21" t="n">
         <v>56905</v>
@@ -3311,10 +3297,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>648899</v>
+        <v>648902</v>
       </c>
       <c r="R21" t="n">
-        <v>6680777</v>
+        <v>6680769</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -3341,22 +3327,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3382,13 +3368,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127772505</t>
+          <t>https://artportalen.se/Sighting/127752094</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128335394</v>
+        <v>127772505</v>
       </c>
       <c r="B22" t="n">
         <v>56905</v>
@@ -3428,17 +3414,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>på övervintringsplats</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3447,10 +3428,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>648814</v>
+        <v>648899</v>
       </c>
       <c r="R22" t="n">
-        <v>6680586</v>
+        <v>6680777</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -3477,22 +3458,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3518,13 +3499,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128335394</t>
+          <t>https://artportalen.se/Sighting/127772505</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128352588</v>
+        <v>128335394</v>
       </c>
       <c r="B23" t="n">
         <v>56905</v>
@@ -3554,7 +3535,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3569,7 +3550,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -3583,10 +3564,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>648813</v>
+        <v>648814</v>
       </c>
       <c r="R23" t="n">
-        <v>6680588</v>
+        <v>6680586</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3613,22 +3594,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3654,13 +3635,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128352588</t>
+          <t>https://artportalen.se/Sighting/128335394</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128429347</v>
+        <v>128352588</v>
       </c>
       <c r="B24" t="n">
         <v>56905</v>
@@ -3705,7 +3686,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -3719,10 +3700,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>648818</v>
+        <v>648813</v>
       </c>
       <c r="R24" t="n">
-        <v>6680594</v>
+        <v>6680588</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3749,22 +3730,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3790,13 +3771,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128429347</t>
+          <t>https://artportalen.se/Sighting/128352588</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128485895</v>
+        <v>128429347</v>
       </c>
       <c r="B25" t="n">
         <v>56905</v>
@@ -3826,7 +3807,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3836,12 +3817,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3855,10 +3836,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>649040</v>
+        <v>648818</v>
       </c>
       <c r="R25" t="n">
-        <v>6680517</v>
+        <v>6680594</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3885,22 +3866,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3926,13 +3907,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128485895</t>
+          <t>https://artportalen.se/Sighting/128429347</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128536947</v>
+        <v>128485895</v>
       </c>
       <c r="B26" t="n">
         <v>56905</v>
@@ -3991,10 +3972,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>648815</v>
+        <v>649040</v>
       </c>
       <c r="R26" t="n">
-        <v>6680595</v>
+        <v>6680517</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -4021,22 +4002,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4062,16 +4043,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128536947</t>
+          <t>https://artportalen.se/Sighting/128485895</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128609972</v>
+        <v>128536947</v>
       </c>
       <c r="B27" t="n">
-        <v>56925</v>
+        <v>56905</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4108,12 +4089,12 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -4121,17 +4102,16 @@
           <t>på övervintringsplats</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tobokrysset, Tobokrysset, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>648842</v>
+        <v>648815</v>
       </c>
       <c r="R27" t="n">
-        <v>6680576</v>
+        <v>6680595</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -4158,22 +4138,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4182,7 +4162,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -4200,13 +4179,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128609972</t>
+          <t>https://artportalen.se/Sighting/128536947</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131559407</v>
+        <v>128609972</v>
       </c>
       <c r="B28" t="n">
         <v>56925</v>
@@ -4266,10 +4245,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>648818</v>
+        <v>648842</v>
       </c>
       <c r="R28" t="n">
-        <v>6680591</v>
+        <v>6680576</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -4296,22 +4275,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4338,13 +4317,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131559407</t>
+          <t>https://artportalen.se/Sighting/128609972</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131594198</v>
+        <v>131559407</v>
       </c>
       <c r="B29" t="n">
         <v>56925</v>
@@ -4404,10 +4383,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>648815</v>
+        <v>648818</v>
       </c>
       <c r="R29" t="n">
-        <v>6680592</v>
+        <v>6680591</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -4434,22 +4413,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4476,13 +4455,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131594198</t>
+          <t>https://artportalen.se/Sighting/131559407</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131594284</v>
+        <v>131594198</v>
       </c>
       <c r="B30" t="n">
         <v>56925</v>
@@ -4542,10 +4521,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>648847</v>
+        <v>648815</v>
       </c>
       <c r="R30" t="n">
-        <v>6680578</v>
+        <v>6680592</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -4577,7 +4556,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4587,7 +4566,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4614,13 +4593,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131594284</t>
+          <t>https://artportalen.se/Sighting/131594198</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131682802</v>
+        <v>131594284</v>
       </c>
       <c r="B31" t="n">
         <v>56925</v>
@@ -4680,10 +4659,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>648815</v>
+        <v>648847</v>
       </c>
       <c r="R31" t="n">
-        <v>6680594</v>
+        <v>6680578</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -4710,22 +4689,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4752,13 +4731,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131682802</t>
+          <t>https://artportalen.se/Sighting/131594284</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131724573</v>
+        <v>131682802</v>
       </c>
       <c r="B32" t="n">
         <v>56925</v>
@@ -4811,16 +4790,17 @@
           <t>på övervintringsplats</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Tobokrysset, Tobokrysset, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>648844</v>
+        <v>648815</v>
       </c>
       <c r="R32" t="n">
-        <v>6680577</v>
+        <v>6680594</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -4847,22 +4827,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4871,6 +4851,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4888,13 +4869,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131724573</t>
+          <t>https://artportalen.se/Sighting/131682802</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131756849</v>
+        <v>131724573</v>
       </c>
       <c r="B33" t="n">
         <v>56925</v>
@@ -4953,10 +4934,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>648812</v>
+        <v>648844</v>
       </c>
       <c r="R33" t="n">
-        <v>6680590</v>
+        <v>6680577</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4983,22 +4964,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5024,13 +5005,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131756849</t>
+          <t>https://artportalen.se/Sighting/131724573</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131843901</v>
+        <v>131756849</v>
       </c>
       <c r="B34" t="n">
         <v>56925</v>
@@ -5060,7 +5041,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -5083,17 +5064,16 @@
           <t>på övervintringsplats</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Tobokrysset, Tobokrysset, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>648809</v>
+        <v>648812</v>
       </c>
       <c r="R34" t="n">
-        <v>6680587</v>
+        <v>6680590</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -5120,22 +5100,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5144,7 +5124,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -5162,13 +5141,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131843901</t>
+          <t>https://artportalen.se/Sighting/131756849</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131946905</v>
+        <v>131843901</v>
       </c>
       <c r="B35" t="n">
         <v>56925</v>
@@ -5198,7 +5177,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5221,13 +5200,14 @@
           <t>på övervintringsplats</t>
         </is>
       </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Tobokrysset, Tobokrysset, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>648844</v>
+        <v>648809</v>
       </c>
       <c r="R35" t="n">
         <v>6680587</v>
@@ -5257,22 +5237,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5281,6 +5261,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -5298,13 +5279,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131946905</t>
+          <t>https://artportalen.se/Sighting/131843901</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131946969</v>
+        <v>131946905</v>
       </c>
       <c r="B36" t="n">
         <v>56925</v>
@@ -5363,10 +5344,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>648857</v>
+        <v>648844</v>
       </c>
       <c r="R36" t="n">
-        <v>6680579</v>
+        <v>6680587</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -5398,7 +5379,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5408,7 +5389,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5434,13 +5415,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131946969</t>
+          <t>https://artportalen.se/Sighting/131946905</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131947112</v>
+        <v>131946969</v>
       </c>
       <c r="B37" t="n">
         <v>56925</v>
@@ -5470,7 +5451,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5499,7 +5480,7 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>648858</v>
+        <v>648857</v>
       </c>
       <c r="R37" t="n">
         <v>6680579</v>
@@ -5534,7 +5515,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5544,7 +5525,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5570,13 +5551,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131947112</t>
+          <t>https://artportalen.se/Sighting/131946969</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132062948</v>
+        <v>131947112</v>
       </c>
       <c r="B38" t="n">
         <v>56925</v>
@@ -5606,7 +5587,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5635,10 +5616,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>648849</v>
+        <v>648858</v>
       </c>
       <c r="R38" t="n">
-        <v>6680585</v>
+        <v>6680579</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -5665,22 +5646,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5706,13 +5687,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132062948</t>
+          <t>https://artportalen.se/Sighting/131947112</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132084479</v>
+        <v>132062948</v>
       </c>
       <c r="B39" t="n">
         <v>56925</v>
@@ -5771,7 +5752,7 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>648845</v>
+        <v>648849</v>
       </c>
       <c r="R39" t="n">
         <v>6680585</v>
@@ -5801,22 +5782,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5842,13 +5823,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132084479</t>
+          <t>https://artportalen.se/Sighting/132062948</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132287989</v>
+        <v>132084479</v>
       </c>
       <c r="B40" t="n">
         <v>56925</v>
@@ -5878,7 +5859,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5907,10 +5888,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>648844</v>
+        <v>648845</v>
       </c>
       <c r="R40" t="n">
-        <v>6680582</v>
+        <v>6680585</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -5937,22 +5918,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5978,13 +5959,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132287989</t>
+          <t>https://artportalen.se/Sighting/132084479</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132315577</v>
+        <v>132287989</v>
       </c>
       <c r="B41" t="n">
         <v>56925</v>
@@ -6043,7 +6024,7 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>648841</v>
+        <v>648844</v>
       </c>
       <c r="R41" t="n">
         <v>6680582</v>
@@ -6073,22 +6054,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6114,13 +6095,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132315577</t>
+          <t>https://artportalen.se/Sighting/132287989</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132441041</v>
+        <v>132315577</v>
       </c>
       <c r="B42" t="n">
         <v>56925</v>
@@ -6150,7 +6131,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -6179,10 +6160,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>648816</v>
+        <v>648841</v>
       </c>
       <c r="R42" t="n">
-        <v>6680584</v>
+        <v>6680582</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -6209,22 +6190,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6250,13 +6231,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132441041</t>
+          <t>https://artportalen.se/Sighting/132315577</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132441132</v>
+        <v>132441041</v>
       </c>
       <c r="B43" t="n">
         <v>56925</v>
@@ -6315,7 +6296,7 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>648846</v>
+        <v>648816</v>
       </c>
       <c r="R43" t="n">
         <v>6680584</v>
@@ -6350,7 +6331,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6360,7 +6341,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6386,13 +6367,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132441132</t>
+          <t>https://artportalen.se/Sighting/132441041</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132463616</v>
+        <v>132441132</v>
       </c>
       <c r="B44" t="n">
         <v>56925</v>
@@ -6422,7 +6403,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -6451,10 +6432,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>648816</v>
+        <v>648846</v>
       </c>
       <c r="R44" t="n">
-        <v>6680590</v>
+        <v>6680584</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -6481,22 +6462,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6522,13 +6503,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132463616</t>
+          <t>https://artportalen.se/Sighting/132441132</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132490522</v>
+        <v>132463616</v>
       </c>
       <c r="B45" t="n">
         <v>56925</v>
@@ -6558,7 +6539,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6587,10 +6568,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>648813</v>
+        <v>648816</v>
       </c>
       <c r="R45" t="n">
-        <v>6680595</v>
+        <v>6680590</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -6617,22 +6598,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6658,13 +6639,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132490522</t>
+          <t>https://artportalen.se/Sighting/132463616</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132490571</v>
+        <v>132490522</v>
       </c>
       <c r="B46" t="n">
         <v>56925</v>
@@ -6694,7 +6675,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6723,10 +6704,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>648843</v>
+        <v>648813</v>
       </c>
       <c r="R46" t="n">
-        <v>6680580</v>
+        <v>6680595</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
@@ -6758,7 +6739,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6768,7 +6749,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6794,13 +6775,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132490571</t>
+          <t>https://artportalen.se/Sighting/132490522</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132520488</v>
+        <v>132490571</v>
       </c>
       <c r="B47" t="n">
         <v>56925</v>
@@ -6859,10 +6840,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>648836</v>
+        <v>648843</v>
       </c>
       <c r="R47" t="n">
-        <v>6680570</v>
+        <v>6680580</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -6889,22 +6870,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6930,16 +6911,16 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132520488</t>
+          <t>https://artportalen.se/Sighting/132490571</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135760499</v>
+        <v>132520488</v>
       </c>
       <c r="B48" t="n">
-        <v>56943</v>
+        <v>56925</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6981,12 +6962,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>på övervintringsplats</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6995,10 +6976,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>648896</v>
+        <v>648836</v>
       </c>
       <c r="R48" t="n">
-        <v>6680771</v>
+        <v>6680570</v>
       </c>
       <c r="S48" t="n">
         <v>1</v>
@@ -7025,22 +7006,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7065,6 +7046,142 @@
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132520488</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>135760499</v>
+      </c>
+      <c r="B49" t="n">
+        <v>56943</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>208260</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Vipera berus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Tobokrysset, Tobokrysset, Upl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>648896</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6680771</v>
+      </c>
+      <c r="S49" t="n">
+        <v>1</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Anders Wahlström</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Anders Wahlström</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135760499</t>
         </is>
@@ -7119,6 +7236,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29320-2026 artfynd.xlsx
+++ b/artfynd/A 29320-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ49"/>
+  <dimension ref="A1:AZ50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2840,7 +2840,7 @@
         <v>137422894</v>
       </c>
       <c r="B18" t="n">
-        <v>58876</v>
+        <v>58879</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3096,10 +3096,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>115538367</v>
+        <v>137525258</v>
       </c>
       <c r="B20" t="n">
-        <v>56905</v>
+        <v>56958</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3107,63 +3107,41 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>208260</v>
+        <v>208257</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tobokrysset, Upl</t>
+          <t>Tegelsmoraån, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>649066</v>
+        <v>649006</v>
       </c>
       <c r="R20" t="n">
-        <v>6680538</v>
+        <v>6680632</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -3190,27 +3168,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Finns utmed järnvägen från korset och 300 meter utmed  traktorspåret.</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3219,7 +3192,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3237,13 +3209,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115538367</t>
+          <t>https://artportalen.se/Sighting/137525258</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127752094</v>
+        <v>115538367</v>
       </c>
       <c r="B21" t="n">
         <v>56905</v>
@@ -3273,7 +3245,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3283,7 +3255,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -3291,16 +3268,21 @@
           <t>vilande</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Tobokrysset, Tobokrysset, Upl</t>
+          <t>Tobokrysset, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>648902</v>
+        <v>649066</v>
       </c>
       <c r="R21" t="n">
-        <v>6680769</v>
+        <v>6680538</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -3327,22 +3309,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Finns utmed järnvägen från korset och 300 meter utmed  traktorspåret.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3351,6 +3338,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3368,13 +3356,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127752094</t>
+          <t>https://artportalen.se/Sighting/115538367</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127772505</v>
+        <v>127752094</v>
       </c>
       <c r="B22" t="n">
         <v>56905</v>
@@ -3428,10 +3416,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>648899</v>
+        <v>648902</v>
       </c>
       <c r="R22" t="n">
-        <v>6680777</v>
+        <v>6680769</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -3458,22 +3446,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3499,13 +3487,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127772505</t>
+          <t>https://artportalen.se/Sighting/127752094</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128335394</v>
+        <v>127772505</v>
       </c>
       <c r="B23" t="n">
         <v>56905</v>
@@ -3545,17 +3533,12 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>på övervintringsplats</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3564,10 +3547,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>648814</v>
+        <v>648899</v>
       </c>
       <c r="R23" t="n">
-        <v>6680586</v>
+        <v>6680777</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3594,22 +3577,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3635,13 +3618,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128335394</t>
+          <t>https://artportalen.se/Sighting/127772505</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128352588</v>
+        <v>128335394</v>
       </c>
       <c r="B24" t="n">
         <v>56905</v>
@@ -3671,7 +3654,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3686,7 +3669,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -3700,10 +3683,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>648813</v>
+        <v>648814</v>
       </c>
       <c r="R24" t="n">
-        <v>6680588</v>
+        <v>6680586</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3730,22 +3713,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3771,13 +3754,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128352588</t>
+          <t>https://artportalen.se/Sighting/128335394</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128429347</v>
+        <v>128352588</v>
       </c>
       <c r="B25" t="n">
         <v>56905</v>
@@ -3822,7 +3805,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3836,10 +3819,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>648818</v>
+        <v>648813</v>
       </c>
       <c r="R25" t="n">
-        <v>6680594</v>
+        <v>6680588</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3866,22 +3849,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3907,13 +3890,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128429347</t>
+          <t>https://artportalen.se/Sighting/128352588</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128485895</v>
+        <v>128429347</v>
       </c>
       <c r="B26" t="n">
         <v>56905</v>
@@ -3943,7 +3926,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3953,12 +3936,12 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3972,10 +3955,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>649040</v>
+        <v>648818</v>
       </c>
       <c r="R26" t="n">
-        <v>6680517</v>
+        <v>6680594</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -4002,22 +3985,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4043,13 +4026,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128485895</t>
+          <t>https://artportalen.se/Sighting/128429347</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128536947</v>
+        <v>128485895</v>
       </c>
       <c r="B27" t="n">
         <v>56905</v>
@@ -4108,10 +4091,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>648815</v>
+        <v>649040</v>
       </c>
       <c r="R27" t="n">
-        <v>6680595</v>
+        <v>6680517</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -4138,22 +4121,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4179,16 +4162,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128536947</t>
+          <t>https://artportalen.se/Sighting/128485895</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128609972</v>
+        <v>128536947</v>
       </c>
       <c r="B28" t="n">
-        <v>56925</v>
+        <v>56905</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4225,12 +4208,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -4238,17 +4221,16 @@
           <t>på övervintringsplats</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Tobokrysset, Tobokrysset, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>648842</v>
+        <v>648815</v>
       </c>
       <c r="R28" t="n">
-        <v>6680576</v>
+        <v>6680595</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -4275,22 +4257,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4299,7 +4281,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4317,13 +4298,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128609972</t>
+          <t>https://artportalen.se/Sighting/128536947</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131559407</v>
+        <v>128609972</v>
       </c>
       <c r="B29" t="n">
         <v>56925</v>
@@ -4383,10 +4364,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>648818</v>
+        <v>648842</v>
       </c>
       <c r="R29" t="n">
-        <v>6680591</v>
+        <v>6680576</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -4413,22 +4394,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4455,13 +4436,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131559407</t>
+          <t>https://artportalen.se/Sighting/128609972</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131594198</v>
+        <v>131559407</v>
       </c>
       <c r="B30" t="n">
         <v>56925</v>
@@ -4521,10 +4502,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>648815</v>
+        <v>648818</v>
       </c>
       <c r="R30" t="n">
-        <v>6680592</v>
+        <v>6680591</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -4551,22 +4532,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4593,13 +4574,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131594198</t>
+          <t>https://artportalen.se/Sighting/131559407</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131594284</v>
+        <v>131594198</v>
       </c>
       <c r="B31" t="n">
         <v>56925</v>
@@ -4659,10 +4640,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>648847</v>
+        <v>648815</v>
       </c>
       <c r="R31" t="n">
-        <v>6680578</v>
+        <v>6680592</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -4694,7 +4675,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4704,7 +4685,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4731,13 +4712,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131594284</t>
+          <t>https://artportalen.se/Sighting/131594198</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131682802</v>
+        <v>131594284</v>
       </c>
       <c r="B32" t="n">
         <v>56925</v>
@@ -4797,10 +4778,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>648815</v>
+        <v>648847</v>
       </c>
       <c r="R32" t="n">
-        <v>6680594</v>
+        <v>6680578</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -4827,22 +4808,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4869,13 +4850,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131682802</t>
+          <t>https://artportalen.se/Sighting/131594284</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131724573</v>
+        <v>131682802</v>
       </c>
       <c r="B33" t="n">
         <v>56925</v>
@@ -4928,16 +4909,17 @@
           <t>på övervintringsplats</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Tobokrysset, Tobokrysset, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>648844</v>
+        <v>648815</v>
       </c>
       <c r="R33" t="n">
-        <v>6680577</v>
+        <v>6680594</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4964,22 +4946,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4988,6 +4970,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -5005,13 +4988,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131724573</t>
+          <t>https://artportalen.se/Sighting/131682802</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131756849</v>
+        <v>131724573</v>
       </c>
       <c r="B34" t="n">
         <v>56925</v>
@@ -5070,10 +5053,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>648812</v>
+        <v>648844</v>
       </c>
       <c r="R34" t="n">
-        <v>6680590</v>
+        <v>6680577</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -5100,22 +5083,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5141,13 +5124,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131756849</t>
+          <t>https://artportalen.se/Sighting/131724573</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131843901</v>
+        <v>131756849</v>
       </c>
       <c r="B35" t="n">
         <v>56925</v>
@@ -5177,7 +5160,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5200,17 +5183,16 @@
           <t>på övervintringsplats</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Tobokrysset, Tobokrysset, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>648809</v>
+        <v>648812</v>
       </c>
       <c r="R35" t="n">
-        <v>6680587</v>
+        <v>6680590</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -5237,22 +5219,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5261,7 +5243,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -5279,13 +5260,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131843901</t>
+          <t>https://artportalen.se/Sighting/131756849</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131946905</v>
+        <v>131843901</v>
       </c>
       <c r="B36" t="n">
         <v>56925</v>
@@ -5315,7 +5296,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5338,13 +5319,14 @@
           <t>på övervintringsplats</t>
         </is>
       </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Tobokrysset, Tobokrysset, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>648844</v>
+        <v>648809</v>
       </c>
       <c r="R36" t="n">
         <v>6680587</v>
@@ -5374,22 +5356,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5398,6 +5380,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -5415,13 +5398,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131946905</t>
+          <t>https://artportalen.se/Sighting/131843901</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131946969</v>
+        <v>131946905</v>
       </c>
       <c r="B37" t="n">
         <v>56925</v>
@@ -5480,10 +5463,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>648857</v>
+        <v>648844</v>
       </c>
       <c r="R37" t="n">
-        <v>6680579</v>
+        <v>6680587</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -5515,7 +5498,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5525,7 +5508,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5551,13 +5534,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131946969</t>
+          <t>https://artportalen.se/Sighting/131946905</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131947112</v>
+        <v>131946969</v>
       </c>
       <c r="B38" t="n">
         <v>56925</v>
@@ -5587,7 +5570,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5616,7 +5599,7 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>648858</v>
+        <v>648857</v>
       </c>
       <c r="R38" t="n">
         <v>6680579</v>
@@ -5651,7 +5634,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5661,7 +5644,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5687,13 +5670,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131947112</t>
+          <t>https://artportalen.se/Sighting/131946969</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132062948</v>
+        <v>131947112</v>
       </c>
       <c r="B39" t="n">
         <v>56925</v>
@@ -5723,7 +5706,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5752,10 +5735,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>648849</v>
+        <v>648858</v>
       </c>
       <c r="R39" t="n">
-        <v>6680585</v>
+        <v>6680579</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -5782,22 +5765,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5823,13 +5806,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132062948</t>
+          <t>https://artportalen.se/Sighting/131947112</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132084479</v>
+        <v>132062948</v>
       </c>
       <c r="B40" t="n">
         <v>56925</v>
@@ -5888,7 +5871,7 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>648845</v>
+        <v>648849</v>
       </c>
       <c r="R40" t="n">
         <v>6680585</v>
@@ -5918,22 +5901,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5959,13 +5942,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132084479</t>
+          <t>https://artportalen.se/Sighting/132062948</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132287989</v>
+        <v>132084479</v>
       </c>
       <c r="B41" t="n">
         <v>56925</v>
@@ -5995,7 +5978,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -6024,10 +6007,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>648844</v>
+        <v>648845</v>
       </c>
       <c r="R41" t="n">
-        <v>6680582</v>
+        <v>6680585</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -6054,22 +6037,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6095,13 +6078,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132287989</t>
+          <t>https://artportalen.se/Sighting/132084479</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132315577</v>
+        <v>132287989</v>
       </c>
       <c r="B42" t="n">
         <v>56925</v>
@@ -6160,7 +6143,7 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>648841</v>
+        <v>648844</v>
       </c>
       <c r="R42" t="n">
         <v>6680582</v>
@@ -6190,22 +6173,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6231,13 +6214,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132315577</t>
+          <t>https://artportalen.se/Sighting/132287989</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132441041</v>
+        <v>132315577</v>
       </c>
       <c r="B43" t="n">
         <v>56925</v>
@@ -6267,7 +6250,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6296,10 +6279,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>648816</v>
+        <v>648841</v>
       </c>
       <c r="R43" t="n">
-        <v>6680584</v>
+        <v>6680582</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -6326,22 +6309,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6367,13 +6350,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132441041</t>
+          <t>https://artportalen.se/Sighting/132315577</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132441132</v>
+        <v>132441041</v>
       </c>
       <c r="B44" t="n">
         <v>56925</v>
@@ -6432,7 +6415,7 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>648846</v>
+        <v>648816</v>
       </c>
       <c r="R44" t="n">
         <v>6680584</v>
@@ -6467,7 +6450,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6477,7 +6460,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6503,13 +6486,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132441132</t>
+          <t>https://artportalen.se/Sighting/132441041</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132463616</v>
+        <v>132441132</v>
       </c>
       <c r="B45" t="n">
         <v>56925</v>
@@ -6539,7 +6522,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6568,10 +6551,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>648816</v>
+        <v>648846</v>
       </c>
       <c r="R45" t="n">
-        <v>6680590</v>
+        <v>6680584</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -6598,22 +6581,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6639,13 +6622,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132463616</t>
+          <t>https://artportalen.se/Sighting/132441132</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132490522</v>
+        <v>132463616</v>
       </c>
       <c r="B46" t="n">
         <v>56925</v>
@@ -6675,7 +6658,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6704,10 +6687,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>648813</v>
+        <v>648816</v>
       </c>
       <c r="R46" t="n">
-        <v>6680595</v>
+        <v>6680590</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
@@ -6734,22 +6717,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6775,13 +6758,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132490522</t>
+          <t>https://artportalen.se/Sighting/132463616</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132490571</v>
+        <v>132490522</v>
       </c>
       <c r="B47" t="n">
         <v>56925</v>
@@ -6811,7 +6794,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6840,10 +6823,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>648843</v>
+        <v>648813</v>
       </c>
       <c r="R47" t="n">
-        <v>6680580</v>
+        <v>6680595</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -6875,7 +6858,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6885,7 +6868,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6911,13 +6894,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132490571</t>
+          <t>https://artportalen.se/Sighting/132490522</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132520488</v>
+        <v>132490571</v>
       </c>
       <c r="B48" t="n">
         <v>56925</v>
@@ -6976,10 +6959,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>648836</v>
+        <v>648843</v>
       </c>
       <c r="R48" t="n">
-        <v>6680570</v>
+        <v>6680580</v>
       </c>
       <c r="S48" t="n">
         <v>1</v>
@@ -7006,22 +6989,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7047,16 +7030,16 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132520488</t>
+          <t>https://artportalen.se/Sighting/132490571</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135760499</v>
+        <v>132520488</v>
       </c>
       <c r="B49" t="n">
-        <v>56943</v>
+        <v>56925</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7098,12 +7081,12 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>på övervintringsplats</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -7112,10 +7095,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>648896</v>
+        <v>648836</v>
       </c>
       <c r="R49" t="n">
-        <v>6680771</v>
+        <v>6680570</v>
       </c>
       <c r="S49" t="n">
         <v>1</v>
@@ -7142,22 +7125,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7182,6 +7165,142 @@
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132520488</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135760499</v>
+      </c>
+      <c r="B50" t="n">
+        <v>56943</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>208260</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Vipera berus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Tobokrysset, Tobokrysset, Upl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>648896</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6680771</v>
+      </c>
+      <c r="S50" t="n">
+        <v>1</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Anders Wahlström</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Anders Wahlström</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135760499</t>
         </is>
@@ -7237,6 +7356,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
